--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/OKLAHOMA_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/OKLAHOMA_2016.xlsx
@@ -3516,7 +3516,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C176">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C280">
@@ -5773,7 +5773,7 @@
         <v>93</v>
       </c>
       <c r="D301">
-        <v>0.009153543307086615</v>
+        <v>0.009153543307086617</v>
       </c>
     </row>
     <row r="302">
@@ -11317,7 +11317,7 @@
         <v>99</v>
       </c>
       <c r="D609">
-        <v>0.009744094488188977</v>
+        <v>0.009744094488188975</v>
       </c>
     </row>
     <row r="610">
@@ -12336,7 +12336,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C666">
@@ -15025,7 +15025,7 @@
         <v>93</v>
       </c>
       <c r="D815">
-        <v>0.009153543307086615</v>
+        <v>0.009153543307086617</v>
       </c>
     </row>
     <row r="816">
@@ -19057,7 +19057,7 @@
         <v>98</v>
       </c>
       <c r="D1039">
-        <v>0.009645669291338583</v>
+        <v>0.009645669291338584</v>
       </c>
     </row>
     <row r="1040">
